--- a/datasets/dict/dict_ps_df003.xlsx
+++ b/datasets/dict/dict_ps_df003.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E61025-DB20-8041-B0C3-679BC5A46F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E249E6A-D5F7-8F45-953C-10B1F7F0D9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
@@ -879,7 +879,7 @@
         <v>36</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -909,7 +909,7 @@
         <v>36</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>2</v>

--- a/datasets/dict/dict_ps_df003.xlsx
+++ b/datasets/dict/dict_ps_df003.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E249E6A-D5F7-8F45-953C-10B1F7F0D9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E32E39-1481-134A-B173-C99B435E1780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="detect_rules" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">detect_rules!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">detect_rules!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">items!$A$1:$A$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="63">
   <si>
     <t>ps_id</t>
   </si>
@@ -222,6 +222,10 @@
   </si>
   <si>
     <t>ps_comp_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>context_chars</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -957,7 +961,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="9" customWidth="1"/>
@@ -965,15 +969,15 @@
     <col min="3" max="3" width="15.42578125" style="9" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" style="9" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="13" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="47.42578125" style="13" customWidth="1"/>
-    <col min="8" max="8" width="9" style="11" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" style="9" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" style="13" customWidth="1"/>
-    <col min="11" max="11" width="127.85546875" style="13" customWidth="1"/>
+    <col min="6" max="7" width="16.42578125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="47.42578125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="9" style="11" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" style="13" customWidth="1"/>
+    <col min="12" max="12" width="127.85546875" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19" customHeight="1">
+    <row r="1" spans="1:12" ht="19" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -992,23 +996,26 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="K1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="9" t="s">
         <v>41</v>
       </c>
@@ -1025,17 +1032,18 @@
         <v>12</v>
       </c>
       <c r="F2" s="9"/>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="9"/>
+      <c r="H2" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="9">
+      <c r="I2" s="9">
         <v>10</v>
       </c>
-      <c r="I2" s="9" t="b">
+      <c r="J2" s="9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="38">
+    <row r="3" spans="1:12" ht="38">
       <c r="A3" s="9" t="s">
         <v>41</v>
       </c>
@@ -1054,22 +1062,23 @@
       <c r="F3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="9">
+      <c r="I3" s="9">
         <v>5</v>
       </c>
-      <c r="I3" s="9" t="b">
+      <c r="J3" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="14"/>
+      <c r="L3" s="14" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
